--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{FBBFB409-76BC-4F46-B485-6EB3092ED8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C58D87DE-140A-440A-9837-8BF6100AE1E7}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{FBBFB409-76BC-4F46-B485-6EB3092ED8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04CEFB12-213E-425C-AF3E-F8837CA186DC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,10 +168,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>HS CODE</t>
-  </si>
-  <si>
-    <t/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -320,7 +321,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -511,15 +512,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -528,7 +520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -623,27 +615,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
@@ -654,6 +628,9 @@
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -700,26 +677,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -771,17 +736,35 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1209,15 +1192,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43"/>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1225,12 +1208,12 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -1247,13 +1230,13 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="57"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
       <c r="F4" s="17" t="s">
         <v>2</v>
       </c>
@@ -1265,13 +1248,13 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="74"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="65"/>
       <c r="F5" s="31" t="s">
         <v>32</v>
       </c>
@@ -1281,147 +1264,147 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="75"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="62" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="57"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="52"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="76"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="49"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="44"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="49"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="44"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="72"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="49"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="44"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="72"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="49"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="44"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="46"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="62" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="57"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="50"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="45"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="49"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="49"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="44"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="46"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="60"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="11" t="s">
         <v>13</v>
       </c>
@@ -1445,15 +1428,15 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="34" t="s">
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="84" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="84" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="26" t="s">
@@ -1471,107 +1454,107 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="42"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="28"/>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="H19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="I19" s="32" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="92" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="37">
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="86"/>
+      <c r="F20" s="87">
         <v>1</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="33">
+      <c r="G20" s="88"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="90">
         <v>0.01</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="69" t="s">
+      <c r="A21" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="33"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="90"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="33"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="90"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="93"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="37"/>
       <c r="E23" s="30"/>
-      <c r="F23" s="41">
+      <c r="F23" s="35">
         <f>SUM(F20:F22)</f>
         <v>1</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="34">
         <f>SUM(G20:G22)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="40"/>
-      <c r="I23" s="39"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="33"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1595,17 +1578,17 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1625,12 +1608,12 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -1639,12 +1622,12 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
@@ -1653,12 +1636,12 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -1667,14 +1650,14 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="44"/>
-      <c r="C36" s="64">
+      <c r="B36" s="39"/>
+      <c r="C36" s="59">
         <v>8116409</v>
       </c>
-      <c r="D36" s="44"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -1683,12 +1666,12 @@
       <c r="J36" s="6"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="64" t="s">
+      <c r="A37" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="44"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="44"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -1697,12 +1680,12 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="64" t="s">
+      <c r="A38" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="44"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="44"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -1748,12 +1731,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A24:I24"/>
@@ -1774,6 +1751,11 @@
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A5:E7"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="E2:H2"/>
@@ -1786,10 +1768,11 @@
     <mergeCell ref="F12:G13"/>
     <mergeCell ref="F6:I6"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
